--- a/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TESTING_TYPES.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TESTING_TYPES.xlsx
@@ -453,19 +453,19 @@
         <v>Kiểm thử tĩnh (Static Testing) bao gồm duyệt tài liệu yêu cầu, duyệt code (code review) để tìm lỗi logic/cú pháp mà không chạy phần mềm. Kiểm thử động (Dynamic Testing) bắt buộc phải nạp code chạy thực tế để đối chiếu kết quả.</v>
       </c>
       <c r="E2" t="str">
+        <v>Kiểm thử tĩnh do QA thực hiện; Kiểm thử động do lập trình viên tự thực hiện trên máy chủ — phân chia vai trò</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Kiểm thử tĩnh hoàn toàn miễn phí; Kiểm thử động yêu cầu phải mua bản quyền phần mềm đắt tiền — so sánh chi phí</v>
+      </c>
+      <c r="G2" t="str">
         <v>Kiểm thử tĩnh kiểm tra tài liệu, mã nguồn mà không chạy chương trình (như review, walkthrough); Kiểm thử động yêu cầu chạy phần mềm để kiểm tra hành vi — không chạy code vs chạy code</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>Kiểm thử tĩnh chỉ áp dụng cho trang web tĩnh HTML; Kiểm thử động áp dụng cho trang web có hoạt ảnh CSS — phân loại theo hiệu ứng</v>
       </c>
-      <c r="G2" t="str">
-        <v>Kiểm thử tĩnh do QA thực hiện; Kiểm thử động do lập trình viên tự thực hiện trên máy chủ — phân chia vai trò</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Kiểm thử tĩnh hoàn toàn miễn phí; Kiểm thử động yêu cầu phải mua bản quyền phần mềm đắt tiền — so sánh chi phí</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Smoke Test (hoặc Build Verification Test) chạy nhanh một bộ test case cơ bản (như đăng nhập, mở trang chủ) để quyết định xem bản build này có đủ ổn định để đội test nhận vào chạy các bộ test chi tiết hay không, tránh lãng phí thời gian nếu bản build bị lỗi sập nguồn ngay lập tức.</v>
       </c>
       <c r="E3" t="str">
-        <v>Thực hiện ngay khi nhận bản build mới để nhanh chóng xác nhận các chức năng cốt lõi nhất có hoạt động bình thường không trước khi test chi tiết — kiểm tra bản build ổn định cơ bản</v>
+        <v>Chỉ thực hiện khi hệ thống cơ sở dữ liệu bị sập hoàn toàn và không thể truy cập được — xử lý sự cố database</v>
       </c>
       <c r="F3" t="str">
         <v>Thực hiện vào cuối dự án để kiểm tra xem hệ thống máy chủ có bị bốc khói do quá tải hay không — kiểm tra nhiệt độ máy chủ</v>
       </c>
       <c r="G3" t="str">
+        <v>Thực hiện ngay khi nhận bản build mới để nhanh chóng xác nhận các chức năng cốt lõi nhất có hoạt động bình thường không trước khi test chi tiết — kiểm tra bản build ổn định cơ bản</v>
+      </c>
+      <c r="H3" t="str">
         <v>Thực hiện trên môi trường của khách hàng để hướng dẫn họ cách cài đặt ứng dụng di động — hướng dẫn cài đặt</v>
       </c>
-      <c r="H3" t="str">
-        <v>Chỉ thực hiện khi hệ thống cơ sở dữ liệu bị sập hoàn toàn và không thể truy cập được — xử lý sự cố database</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Integration Testing (Kiểm thử tích hợp) tập trung kiểm tra giao tiếp, truyền tải dữ liệu (interfaces) giữa các thành phần phần mềm hoặc giữa các hệ thống với nhau.</v>
       </c>
       <c r="E4" t="str">
+        <v>System Testing — Kiểm thử toàn bộ hệ thống hoàn chỉnh từ đầu đến cuối — mức độ hệ thống</v>
+      </c>
+      <c r="F4" t="str">
         <v>Integration Testing — Kiểm thử tích hợp — mức độ tích hợp</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v>Acceptance Testing — Kiểm thử chấp nhận người dùng nghiệm thu sản phẩm — mức độ nghiệm thu</v>
+      </c>
+      <c r="H4" t="str">
         <v>Unit Testing — Kiểm thử đơn vị các hàm, phương thức nhỏ trong code — mức độ đơn vị</v>
       </c>
-      <c r="G4" t="str">
-        <v>System Testing — Kiểm thử toàn bộ hệ thống hoàn chỉnh từ đầu đến cuối — mức độ hệ thống</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Acceptance Testing — Kiểm thử chấp nhận người dùng nghiệm thu sản phẩm — mức độ nghiệm thu</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Functional testing validate các yêu cầu chức năng (đăng nhập, thanh toán). Non-functional testing validate chất lượng vận hành của hệ thống (tốc độ tải trang, khả năng chịu tải, tính bảo mật thông tin).</v>
       </c>
       <c r="E5" t="str">
+        <v>Chức năng chỉ test trên máy tính; Phi chức năng chỉ test trên điện thoại di động di động — phân loại thiết bị test</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Chức năng luôn luôn dễ phát hiện lỗi hơn gấp 10 lần so với phi chức năng — mức độ phát hiện lỗi</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Chức năng do lập trình viên tự test; Phi chức năng bắt buộc phải thuê bên thứ ba độc lập vào test — phân chia vai trò test</v>
+      </c>
+      <c r="H5" t="str">
         <v>Chức năng kiểm tra hệ thống làm ĐƯỢC GÌ (hành vi nghiệp vụ); Phi chức năng kiểm tra hệ thống chạy NHƯ THẾ NÀO (hiệu năng, bảo mật, tính khả dụng) — làm được gì vs chạy như thế nào</v>
       </c>
-      <c r="F5" t="str">
-        <v>Chức năng do lập trình viên tự test; Phi chức năng bắt buộc phải thuê bên thứ ba độc lập vào test — phân chia vai trò test</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Chức năng chỉ test trên máy tính; Phi chức năng chỉ test trên điện thoại di động di động — phân loại thiết bị test</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Chức năng luôn luôn dễ phát hiện lỗi hơn gấp 10 lần so với phi chức năng — mức độ phát hiện lỗi</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Unit Testing đòi hỏi đọc hiểu cấu trúc code ở cấp độ hàm/phương thức chi tiết (White-box testing), do đó lập trình viên phải tự viết các unit test cases (ví dụ dùng JUnit, NUnit, Jest) để chạy kiểm tra trước khi commit code.</v>
       </c>
       <c r="E6" t="str">
+        <v>Project Manager chịu trách nhiệm quản lý chung của dự án — quản lý dự án</v>
+      </c>
+      <c r="F6" t="str">
         <v>Developer (Lập trình viên) trực tiếp viết code của dự án — lập trình viên thực hiện</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>Manual QA (Kiểm thử viên thủ công) chuyên viết test case trên Excel — kiểm thử viên thủ công</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Khách hàng hoặc người dùng cuối ở giai đoạn nghiệm thu bàn giao — người dùng cuối</v>
       </c>
-      <c r="H6" t="str">
-        <v>Project Manager chịu trách nhiệm quản lý chung của dự án — quản lý dự án</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -601,13 +601,13 @@
         <v>Hiểu rõ yêu cầu nghiệp vụ và hành vi bên ngoài của hệ thống mà không cần quan tâm đến cấu trúc code bên trong — hiểu nghiệp vụ hành vi</v>
       </c>
       <c r="F7" t="str">
+        <v>Biết cách cấu hình hệ thống mạng và cài đặt máy chủ vật lý cho công ty — cấu hình máy chủ</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Biết cách thiết kế giao diện đồ họa bằng công cụ Figma hoặc Adobe Photoshop — đồ họa giao diện</v>
+      </c>
+      <c r="H7" t="str">
         <v>Đọc hiểu chi tiết mã nguồn code Java/C# và cấu trúc thuật toán của dev — đọc hiểu mã nguồn</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Biết cách cấu hình hệ thống mạng và cài đặt máy chủ vật lý cho công ty — cấu hình máy chủ</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Biết cách thiết kế giao diện đồ họa bằng công cụ Figma hoặc Adobe Photoshop — đồ họa giao diện</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -630,10 +630,10 @@
         <v>Acceptance Testing — Kiểm thử chấp nhận (nghiệm thu) — mức độ nghiệm thu</v>
       </c>
       <c r="F8" t="str">
+        <v>Integration Testing — Kiểm thử tích hợp các module — mức độ tích hợp</v>
+      </c>
+      <c r="G8" t="str">
         <v>System Testing — Kiểm thử toàn bộ hệ thống tích hợp — mức độ hệ thống</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Integration Testing — Kiểm thử tích hợp các module — mức độ tích hợp</v>
       </c>
       <c r="H8" t="str">
         <v>Unit Testing — Kiểm thử đơn vị các thành phần code — mức độ đơn vị</v>
@@ -656,19 +656,19 @@
         <v>Khi sửa code, dev dễ vô tình làm hỏng logic của các phần khác (side effects). Regression testing chạy lại một bộ test case ở các khu vực liên quan để đảm bảo tính ổn định của hệ thống.</v>
       </c>
       <c r="E9" t="str">
+        <v>Kiểm tra xem hệ thống có bị hack thông qua các cổng mạng đang mở hay không — kiểm thử bảo mật</v>
+      </c>
+      <c r="F9" t="str">
         <v>Đảm bảo các thay đổi mới (sửa lỗi, thêm tính năng) không gây ảnh hưởng xấu (tạo ra lỗi mới) ở các vùng chức năng cũ đang hoạt động ổn định — ngăn chặn tác động phụ</v>
       </c>
-      <c r="F9" t="str">
-        <v>Kiểm tra xem hệ thống có bị hack thông qua các cổng mạng đang mở hay không — kiểm thử bảo mật</v>
-      </c>
       <c r="G9" t="str">
+        <v>Đo lường thời gian phản hồi của trang web khi có đúng 1 người dùng truy cập — kiểm thử hiệu năng tối thiểu</v>
+      </c>
+      <c r="H9" t="str">
         <v>Tính toán tổng số tiền tối đa doanh nghiệp có thể tiết kiệm được nhờ áp dụng phần mềm — tính toán lợi nhuận</v>
       </c>
-      <c r="H9" t="str">
-        <v>Đo lường thời gian phản hồi của trang web khi có đúng 1 người dùng truy cập — kiểm thử hiệu năng tối thiểu</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>System Testing do QA chạy để đảm bảo hệ thống xây đúng thiết kế kỹ thuật (SRS). Acceptance Testing do chính khách hàng/người dùng chạy để xác nhận hệ thống chạy đúng quy trình thực tế của họ và đem lại giá trị kinh doanh.</v>
       </c>
       <c r="E10" t="str">
-        <v>System: Kiểm thử toàn diện chức năng/phi chức năng dựa trên tài liệu SRS kỹ thuật; Acceptance: Kiểm thử dựa trên kịch bản nghiệp vụ thực tế của người dùng cuối để nghiệm thu — đặc tả kỹ thuật vs nghiệp vụ thực tế</v>
+        <v>System do khách hàng thực hiện; còn Acceptance do đội QA của dự án thực hiện — phân chia vai trò thực hiện</v>
       </c>
       <c r="F10" t="str">
-        <v>System do khách hàng thực hiện; còn Acceptance do đội QA của dự án thực hiện — phân chia vai trò thực hiện</v>
+        <v>System chỉ test trên môi trường Staging; còn Acceptance bắt buộc phải chạy thẳng trên Production — phân loại môi trường</v>
       </c>
       <c r="G10" t="str">
         <v>System bắt buộc phải chạy tự động; còn Acceptance bắt buộc phải test thủ công hoàn toàn — phân loại phương pháp test</v>
       </c>
       <c r="H10" t="str">
-        <v>System chỉ test trên môi trường Staging; còn Acceptance bắt buộc phải chạy thẳng trên Production — phân loại môi trường</v>
+        <v>System: Kiểm thử toàn diện chức năng/phi chức năng dựa trên tài liệu SRS kỹ thuật; Acceptance: Kiểm thử dựa trên kịch bản nghiệp vụ thực tế của người dùng cuối để nghiệm thu — đặc tả kỹ thuật vs nghiệp vụ thực tế</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Unit test yêu cầu test nhanh, độc lập. Nếu hàm A gọi Database thực tế, test case sẽ chạy chậm và phụ thuộc vào kết nối DB. Mocking tạo ra một đối tượng DB giả lập trả về kết quả định sẵn để kiểm tra đúng logic nội bộ của hàm A.</v>
       </c>
       <c r="E11" t="str">
-        <v>Cách ly đơn vị code đang kiểm thử (hàm A) khỏi các thành phần phụ thuộc bên ngoài chưa sẵn sàng (như Database, API bên ngoài) bằng cách dùng dữ liệu giả lập — cách ly đơn vị code cần test</v>
+        <v>Tạo ra các giao diện người dùng giả lập có hình vẽ hoạt hình để demo cho khách hàng — giao diện hoạt hình giả lập</v>
       </c>
       <c r="F11" t="str">
         <v>Tự động tăng tốc độ xử lý của vi xử lý máy chủ lên nhanh gấp đôi khi chạy test — tăng tốc độ máy chủ</v>
       </c>
       <c r="G11" t="str">
-        <v>Tạo ra các giao diện người dùng giả lập có hình vẽ hoạt hình để demo cho khách hàng — giao diện hoạt hình giả lập</v>
+        <v>Cách ly đơn vị code đang kiểm thử (hàm A) khỏi các thành phần phụ thuộc bên ngoài chưa sẵn sàng (như Database, API bên ngoài) bằng cách dùng dữ liệu giả lập — cách ly đơn vị code cần test</v>
       </c>
       <c r="H11" t="str">
         <v>Kiểm tra xem hệ thống có bị rò rỉ dữ liệu tài chính ra ngoài mạng internet hay không — kiểm thử rò rỉ dữ liệu</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -746,13 +746,13 @@
         <v>Load: Kiểm tra hệ thống dưới tải lượng người dùng bình thường dự kiến; Stress: Kiểm tra hệ thống dưới tải cực hạn vượt ngưỡng thiết kế để tìm điểm gãy (break point) của hệ thống — tải bình thường vs tải cực hạn tìm điểm gãy</v>
       </c>
       <c r="F12" t="str">
-        <v>Load chỉ dùng cho phần mềm điện thoại di động; còn Stress chỉ dùng cho phần mềm máy tính bàn — phân loại theo thiết bị</v>
+        <v>Load bắt buộc phải chạy ban ngày; còn Stress chỉ được phép chạy vào nửa đêm — giới hạn thời gian chạy test</v>
       </c>
       <c r="G12" t="str">
         <v>Load do lập trình viên tự test; còn Stress bắt buộc phải thuê chuyên gia tâm lý vào đánh giá — phân chia vai trò test</v>
       </c>
       <c r="H12" t="str">
-        <v>Load bắt buộc phải chạy ban ngày; còn Stress chỉ được phép chạy vào nửa đêm — giới hạn thời gian chạy test</v>
+        <v>Load chỉ dùng cho phần mềm điện thoại di động; còn Stress chỉ dùng cho phần mềm máy tính bàn — phân loại theo thiết bị</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -801,19 +801,19 @@
         <v>Component Integration tích hợp các Class/Packages nội bộ trong code. SIT (System Integration Testing) là mức tích hợp cao hơn, kiểm tra xem ứng dụng của bạn có gọi API lấy dữ liệu và gửi nhận tin nhắn thành công với các hệ thống ERP, CRM, Cổng thanh toán của đối tác hay không.</v>
       </c>
       <c r="E14" t="str">
+        <v>SIT chỉ dùng cho các dự án chạy theo mô hình Waterfall; còn Component Integration chỉ dùng cho Agile — phân loại theo mô hình</v>
+      </c>
+      <c r="F14" t="str">
         <v>SIT kiểm tra giao tiếp giữa hệ thống đang phát triển với các hệ thống/ứng dụng bên ngoài khác; Component Integration kiểm tra giao tiếp giữa các module nội bộ bên trong một ứng dụng — tích hợp hệ thống ngoài vs tích hợp module nội bộ</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>SIT do khách hàng tự chạy thủ công; còn Component Integration do đội QA chạy tự động hoàn toàn — chủ thể thực hiện</v>
-      </c>
-      <c r="G14" t="str">
-        <v>SIT chỉ dùng cho các dự án chạy theo mô hình Waterfall; còn Component Integration chỉ dùng cho Agile — phân loại theo mô hình</v>
       </c>
       <c r="H14" t="str">
         <v>SIT bắt buộc phải chạy trên máy chủ Cloud AWS; còn Component Integration chỉ chạy được trên Google Cloud — nền tảng máy chủ</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>Vì nó cho phép Tester tự do kiểm thử dựa trên kinh nghiệm, tư duy phản biện và khám phá hệ thống thời gian thực mà không bị gò bó bởi test case viết sẵn, giúp phát hiện các bug dị biệt — kiểm thử tự do khám phá phát hiện bug ẩn</v>
       </c>
       <c r="F15" t="str">
+        <v>Vì nó bắt buộc Tester phải chạy kiểm thử trên điện thoại di động khi đang di chuyển ngoài đường — kiểm thử di động</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Vì nó loại bỏ hoàn toàn việc phải báo cáo lỗi lên các hệ thống quản lý bug như Jira — loại bỏ báo cáo lỗi</v>
+      </c>
+      <c r="H15" t="str">
         <v>Vì nó tự động hóa 100% việc viết mã nguồn test case bằng trí tuệ nhân tạo AI — tự động viết test case</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Vì nó bắt buộc Tester phải chạy kiểm thử trên điện thoại di động khi đang di chuyển ngoài đường — kiểm thử di động</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Vì nó loại bỏ hoàn toàn việc phải báo cáo lỗi lên các hệ thống quản lý bug như Jira — loại bỏ báo cáo lỗi</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -859,19 +859,19 @@
         <v>Compatibility Testing đảm bảo ứng dụng hiển thị và hoạt động đúng chuẩn trên cả Chrome, Safari, Firefox; trên iOS và Android; trên màn hình nhỏ điện thoại đến màn hình to máy tính.</v>
       </c>
       <c r="E16" t="str">
-        <v>Khả năng phần mềm chạy ổn định và hiển thị đúng trên các cấu hình hệ điều hành, trình duyệt, kích thước màn hình và thiết bị phần cứng khác nhau — tính tương thích đa nền tảng</v>
+        <v>Khả năng kết nối cơ sở dữ liệu quan hệ của hệ thống với hệ quản trị cơ sở dữ liệu NoSQL — tương thích cơ sở dữ liệu</v>
       </c>
       <c r="F16" t="str">
-        <v>Khả năng kết nối cơ sở dữ liệu quan hệ của hệ thống với hệ quản trị cơ sở dữ liệu NoSQL — tương thích cơ sở dữ liệu</v>
+        <v>Khả năng phần mềm tự động nâng cấp phiên bản mới mà không cần người dùng nhấn nút đồng ý — tự động nâng cấp</v>
       </c>
       <c r="G16" t="str">
         <v>Mức độ tương hợp về tính cách giữa lập trình viên và kiểm thử viên trong team — tương hợp nhân sự</v>
       </c>
       <c r="H16" t="str">
-        <v>Khả năng phần mềm tự động nâng cấp phiên bản mới mà không cần người dùng nhấn nút đồng ý — tự động nâng cấp</v>
+        <v>Khả năng phần mềm chạy ổn định và hiển thị đúng trên các cấu hình hệ điều hành, trình duyệt, kích thước màn hình và thiết bị phần cứng khác nhau — tính tương thích đa nền tảng</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -894,10 +894,10 @@
         <v>Vulnerability Scanning do QA tự chạy; còn Penetration Testing do hacker mũ đen tự ý thực hiện bất hợp pháp — tính pháp lý</v>
       </c>
       <c r="G17" t="str">
+        <v>Vulnerability Scanning bắt buộc phải chạy hàng ngày; còn Penetration Testing chỉ chạy 10 năm một lần — giới hạn tần suất chạy</v>
+      </c>
+      <c r="H17" t="str">
         <v>Vulnerability Scanning chỉ áp dụng cho mã nguồn Backend; còn Penetration Testing chỉ áp dụng cho giao diện Frontend — phân loại layer test</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Vulnerability Scanning bắt buộc phải chạy hàng ngày; còn Penetration Testing chỉ chạy 10 năm một lần — giới hạn tần suất chạy</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -917,19 +917,19 @@
         <v>Nghịch lý thuốc trừ sâu chỉ ra rằng nếu dùng mãi 1 loại thuốc, sâu sẽ kháng thuốc (chạy đi chạy lại 1 bộ test case, hệ thống sẽ hết lỗi phát hiện thêm). QA phải liên tục cập nhật bộ test hồi quy để bao phủ các kịch bản mới phát sinh.</v>
       </c>
       <c r="E18" t="str">
+        <v>Tăng gấp đôi tần suất chạy bộ test hồi quy hiện tại lên 2 lần một ngày — tăng tần suất chạy</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Yêu cầu lập trình viên viết code bằng một ngôn ngữ lập trình khác sau mỗi sprint — thay đổi ngôn ngữ code</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Sử dụng các công cụ tự động hóa để chạy ngẫu nhiên các câu lệnh SQL vào database — chạy SQL ngẫu nhiên</v>
+      </c>
+      <c r="H18" t="str">
         <v>Thường xuyên cập nhật, bổ sung các kịch bản test mới và loại bỏ các test case đã lỗi thời khỏi bộ test hồi quy — làm mới bộ test case</v>
       </c>
-      <c r="F18" t="str">
-        <v>Tăng gấp đôi tần suất chạy bộ test hồi quy hiện tại lên 2 lần một ngày — tăng tần suất chạy</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Yêu cầu lập trình viên viết code bằng một ngôn ngữ lập trình khác sau mỗi sprint — thay đổi ngôn ngữ code</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Sử dụng các công cụ tự động hóa để chạy ngẫu nhiên các câu lệnh SQL vào database — chạy SQL ngẫu nhiên</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Kiểm thử hiệu năng cần quy trình bài bản. Load test (mức 10k CCU) kiểm tra khả năng đáp ứng thông thường. Soak test (duy trì tải trong thời gian dài) rất quan trọng để phát hiện lỗi rò rỉ bộ nhớ (Memory leaks) hoặc đầy ổ cứng log. Spike test giả lập giờ cao điểm (ví dụ chuyển khoản nhận lương).</v>
       </c>
       <c r="E19" t="str">
-        <v>Thiết kế kịch bản kiểm thử tải tăng dần (Step-up Load test) lên mốc 10,000 CCU, chạy kiểm thử độ bền (Endurance/Soak test) duy trì trong 12 giờ để kiểm tra rò rỉ bộ nhớ, và chạy kiểm thử đột biến (Spike test) để xem phản hồi của hệ thống khi tải tăng vọt đột ngột — quy trình kiểm thử hiệu năng toàn diện</v>
+        <v>Bỏ qua bước giả lập tải, nén toàn bộ mã nguồn của database và deploy thẳng lên môi trường production chạy thực tế — chạy thực tế rủi ro cực cao</v>
       </c>
       <c r="F19" t="str">
         <v>Sử dụng 10,000 chiếc điện thoại di động vật lý thực tế xếp trên bàn và thuê 10,000 sinh viên cùng nhấn nút chuyển tiền một lúc — giải pháp vật lý bất khả thi</v>
       </c>
       <c r="G19" t="str">
+        <v>Thiết kế kịch bản kiểm thử tải tăng dần (Step-up Load test) lên mốc 10,000 CCU, chạy kiểm thử độ bền (Endurance/Soak test) duy trì trong 12 giờ để kiểm tra rò rỉ bộ nhớ, và chạy kiểm thử đột biến (Spike test) để xem phản hồi của hệ thống khi tải tăng vọt đột ngột — quy trình kiểm thử hiệu năng toàn diện</v>
+      </c>
+      <c r="H19" t="str">
         <v>Chỉ cần chạy thử nghiệm kịch bản với 1 người dùng duy nhất, lấy thời gian phản hồi nhân lên với 10,000 lần — nhân tuyến tính lý thuyết sai lệch</v>
       </c>
-      <c r="H19" t="str">
-        <v>Bỏ qua bước giả lập tải, nén toàn bộ mã nguồn của database và deploy thẳng lên môi trường production chạy thực tế — chạy thực tế rủi ro cực cao</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Trong CI/CD pipeline, tốc độ phản hồi (feedback loop) rất quan trọng. Bắt dev đợi 1-2 tiếng chạy full regression mỗi lần push code sẽ phá vỡ quy trình CI. Chia nhỏ bộ test: PR check chạy nhanh (Smoke/Unit test), còn full test chạy ngầm hàng đêm khi mọi người đã nghỉ là giải pháp tối ưu.</v>
       </c>
       <c r="E20" t="str">
+        <v>Chỉ chạy kiểm thử tự động trên môi trường máy tính cá nhân của Tester và gửi báo cáo qua file chat Skype — chạy test cục bộ</v>
+      </c>
+      <c r="F20" t="str">
         <v>Phân tách test suite thành: Bộ Test khói chạy nhanh (Smoke Test - dưới 5 phút) chạy tự động ở mỗi Pull Request; và Bộ Test hồi quy đầy đủ (Full Regression Suite) chạy tự động hàng đêm (Nightly build) hoặc định kỳ cuối tuần — phân tách bộ test tối ưu CI/CD pipeline</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>Cấu hình cho toàn bộ hệ thống tự động chạy lại tất cả 10,000 test case hồi quy chi tiết mỗi khi developer sửa một dấu chấm hoặc dòng comment trong code — chạy test tối đa gây nghẽn pipeline</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Yêu cầu developers không được phép commit code mới quá 1 lần trong một tuần để dành thời gian cho server chạy test tự động — hạn chế dev commit code</v>
       </c>
-      <c r="H20" t="str">
-        <v>Chỉ chạy kiểm thử tự động trên môi trường máy tính cá nhân của Tester và gửi báo cáo qua file chat Skype — chạy test cục bộ</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>SAST (kiểm thử tĩnh) phát hiện lỗi sớm khi viết code (Shift-left), chỉ ra chính xác dòng code bị hổng bảo mật. DAST (kiểm thử động) phát hiện lỗi khi app đã chạy thực tế (như lỗi xác thực, lỗi SSL, cấu hình API Gateway) mà SAST không thể thấy vì code tĩnh không phản ánh bối cảnh chạy thực tế.</v>
       </c>
       <c r="E21" t="str">
+        <v>SAST chỉ chạy được trên hệ điều hành Windows; còn DAST chỉ chạy được trên hệ điều hành Linux — phân loại theo hệ điều hành</v>
+      </c>
+      <c r="F21" t="str">
+        <v>SAST chỉ test giao diện người dùng Frontend; còn DAST chỉ test cơ sở dữ liệu Backend — phân loại theo layer công nghệ</v>
+      </c>
+      <c r="G21" t="str">
         <v>SAST quét mã nguồn từ bên trong (mã nguồn tĩnh) để tìm lỗ hổng lập trình (như SQL Injection, Buffer Overflow); DAST tấn công giả lập từ bên ngoài vào ứng dụng đang chạy để phát hiện lỗi cấu hình, runtime; kết hợp cả hai để bao phủ tối đa lỗ hổng — SAST quét nguồn vs DAST tấn công runtime</v>
       </c>
-      <c r="F21" t="str">
-        <v>SAST chỉ chạy được trên hệ điều hành Windows; còn DAST chỉ chạy được trên hệ điều hành Linux — phân loại theo hệ điều hành</v>
-      </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>SAST hoàn toàn miễn phí; còn DAST bắt buộc phải thuê hacker mũ đen thực hiện bất hợp pháp — phân loại chi phí pháp lý</v>
       </c>
-      <c r="H21" t="str">
-        <v>SAST chỉ test giao diện người dùng Frontend; còn DAST chỉ test cơ sở dữ liệu Backend — phân loại theo layer công nghệ</v>
-      </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1036,10 +1036,10 @@
         <v>Sử dụng phân tích tác động (Impact Analysis) dựa trên bản vẽ kiến trúc hệ thống và sơ đồ luồng dữ liệu (hoặc xem Git diff code change) để xác định các module phụ thuộc trực tiếp và gián tiếp có sử dụng dữ liệu thuế — phân tích tác động khoanh vùng test</v>
       </c>
       <c r="F22" t="str">
+        <v>Chỉ kiểm thử đúng module tính Thuế vừa được sửa, bỏ qua toàn bộ các module bán hàng, mua hàng, tính lương xung quanh — kiểm thử cục bộ rủi ro cao</v>
+      </c>
+      <c r="G22" t="str">
         <v>Yêu cầu lập trình viên tự viết giấy cam kết rằng code mới của họ không làm hỏng bất kỳ chức năng cũ nào — tin tưởng tuyệt đối lập trình viên</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Chỉ kiểm thử đúng module tính Thuế vừa được sửa, bỏ qua toàn bộ các module bán hàng, mua hàng, tính lương xung quanh — kiểm thử cục bộ rủi ro cao</v>
       </c>
       <c r="H22" t="str">
         <v>Chạy ngẫu nhiên một số test case bất kỳ trong kho dữ liệu mà không cần quan tâm đến tính liên quan của tính năng — chọn test case ngẫu nhiên</v>
@@ -1068,10 +1068,10 @@
         <v>Để đảm bảo phần mềm tự động nén kích thước cơ sở dữ liệu xuống nhỏ hơn 100MB khi có động đất xảy ra — nén dữ liệu khi thiên tai</v>
       </c>
       <c r="G23" t="str">
+        <v>Để bắt buộc lập trình viên phải sao lưu mã nguồn code ra đĩa mềm vật lý và cất trong két sắt an toàn — sao lưu đĩa mềm vật lý</v>
+      </c>
+      <c r="H23" t="str">
         <v>Để kiểm tra xem hệ thống có tự động gửi tin nhắn SMS chúc mừng sinh nhật cho toàn bộ ban giám đốc ngân hàng hay không — tính năng phụ</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Để bắt buộc lập trình viên phải sao lưu mã nguồn code ra đĩa mềm vật lý và cất trong két sắt an toàn — sao lưu đĩa mềm vật lý</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1094,13 +1094,13 @@
         <v>Tách biệt kịch bản test (test logic) ra khỏi dữ liệu test (test data); lưu trữ hàng trăm cặp giá trị đầu vào và kết quả mong đợi trong một file Excel/CSV bên ngoài để script test tự động đọc và chạy lặp lại — tách biệt kịch bản và dữ liệu test</v>
       </c>
       <c r="F24" t="str">
-        <v>Hardcode trực tiếp cả 100 giá trị kiểm thử khác nhau vào bên trong 100 hàm kiểm thử độc lập của mã nguồn code test — hardcode dữ liệu test</v>
+        <v>Xóa bỏ toàn bộ các kịch bản test và chỉ thực hiện test thủ công bằng cách tự gõ tay các giá trị ngẫu nhiên vào form giao diện — thủ công hoàn toàn</v>
       </c>
       <c r="G24" t="str">
         <v>Yêu cầu lập trình viên viết code tự động sinh ra các con số tuổi và giới tính ngẫu nhiên khi chạy chương trình — sinh số ngẫu nhiên</v>
       </c>
       <c r="H24" t="str">
-        <v>Xóa bỏ toàn bộ các kịch bản test và chỉ thực hiện test thủ công bằng cách tự gõ tay các giá trị ngẫu nhiên vào form giao diện — thủ công hoàn toàn</v>
+        <v>Hardcode trực tiếp cả 100 giá trị kiểm thử khác nhau vào bên trong 100 hàm kiểm thử độc lập của mã nguồn code test — hardcode dữ liệu test</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1120,19 +1120,19 @@
         <v>Điện thoại di động là môi trường tương tác năng động, liên tục bị ngắt. Interrupt testing kiểm tra xem app của bạn có bị crash, bị mất dữ liệu đang nhập dở, hoặc bị treo cứng khi có cuộc gọi điện thoại chen ngang hay không, đảm bảo trải nghiệm người dùng mượt mà.</v>
       </c>
       <c r="E25" t="str">
+        <v>Để bắt buộc người dùng phải cắm sạc điện thoại thì mới cho phép mở ứng dụng sử dụng — bắt buộc cắm sạc</v>
+      </c>
+      <c r="F25" t="str">
         <v>Để đánh giá xem ứng dụng xử lý mượt mà thế nào khi có các ngắt hệ thống đột ngột (cuộc gọi đến, tin nhắn SMS, mất kết nối mạng, pin yếu, cắm sạc) và khôi phục đúng trạng thái trước khi bị ngắt — kiểm thử khả năng xử lý ngắt hệ thống di động</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>Để đảm bảo phần mềm tự động chặn toàn bộ các cuộc gọi điện thoại của người dùng khi họ đang mở ứng dụng — chặn cuộc gọi di động</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Để kiểm tra xem ứng dụng có tự động xóa các file ảnh cũ lưu trong thẻ nhớ điện thoại của khách hàng hay không — tự động xóa ảnh thẻ nhớ</v>
       </c>
-      <c r="H25" t="str">
-        <v>Để bắt buộc người dùng phải cắm sạc điện thoại thì mới cho phép mở ứng dụng sử dụng — bắt buộc cắm sạc</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Testing Pyramid của Mike Cohn nhấn mạnh hiệu quả tài chính và thời gian. Unit tests (đáy) chạy chỉ vài mili-giây, giúp dev phát hiện lỗi lập trình ngay lập tức. UI tests (đỉnh) đi qua toàn bộ các tầng nên chạy rất chậm, tốn tài nguyên và dễ gãy (brittle) khi có một thay đổi nhỏ về giao diện, vì vậy chỉ nên dùng để test các luồng nghiệp vụ cốt lõi nhất (End-to-End).</v>
       </c>
       <c r="E26" t="str">
+        <v>Vì Unit Test do robot tự động viết; còn UI Test bắt buộc phải thuê con người chạy thủ công hoàn toàn — robot vs con người</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Vì giao diện người dùng UI không quan trọng đối với sự thành công của sản phẩm phần mềm — UI không quan trọng</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Vì hệ điều hành máy chủ chỉ hỗ trợ chạy Unit Test chứ không hỗ trợ hiển thị giao diện đồ họa — giới hạn máy chủ</v>
+      </c>
+      <c r="H26" t="str">
         <v>Vì Unit Test chạy cực nhanh, chi phí viết/chạy rẻ và cô lập lỗi dễ dàng; UI Test chạy chậm, chi phí cao, dễ bị lỗi ảo (flaky test) do thay đổi giao diện nên cần hạn chế — tối ưu chi phí và tốc độ phản hồi của bộ test</v>
       </c>
-      <c r="F26" t="str">
-        <v>Vì Unit Test do robot tự động viết; còn UI Test bắt buộc phải thuê con người chạy thủ công hoàn toàn — robot vs con người</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Vì giao diện người dùng UI không quan trọng đối với sự thành công của sản phẩm phần mềm — UI không quan trọng</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Vì hệ điều hành máy chủ chỉ hỗ trợ chạy Unit Test chứ không hỗ trợ hiển thị giao diện đồ họa — giới hạn máy chủ</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
